--- a/asignaturas/biologia/propuesta/Propuesta_Biologia_G05-G08.xlsx
+++ b/asignaturas/biologia/propuesta/Propuesta_Biologia_G05-G08.xlsx
@@ -543,11 +543,11 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U5-5.3, G06-CIE-U5-5.6</t>
+          <t>G06-CIE-U5-5.3, G06-CIE-U5-5.6, G06-CIE-U5-5.1, G06-CIE-U5-5.9, G06-CIE-U5-5.8</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>6</v>
@@ -562,27 +562,27 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>7.1. Construcción de una línea temporal sobre el desarrollo de la teoría celular. | 7.2. Representación de los niveles de organización de los seres vivos, de la célula al organismo.</t>
+          <t>7.1. Construcción de una línea temporal sobre el desarrollo de la teoría celular. | 7.2. Representación de los niveles de organización de los seres vivos, de la célula al organismo. | 7.3. Identificación experimental de los grupos de biomoléculas en los alimentos y del carbono como su elemento base. | 7.4. Identificación de las estructuras básicas de la célula: membrana, citoplasma (citosol) y núcleo. | 7.5. Demostración experimental de la difusión y la ósmosis a través de la membrana celular.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Explica con ejemplos que todos los seres vivos están formados por células y ordena en una línea temporal los aportes que llevaron a la teoría celular. | Ordena en un esquema célula, tejido, órgano, sistema y organismo, con un ejemplo de planta y otro de animal.</t>
+          <t>Explica con ejemplos que todos los seres vivos están formados por células y ordena en una línea temporal los aportes que llevaron a la teoría celular. | Ordena en un esquema célula, tejido, órgano, sistema y organismo, con un ejemplo de planta y otro de animal. | Identifica con pruebas sencillas (yodo, papel, Biuret) almidón, grasas y proteínas en alimentos y reconoce el carbono como elemento común a todas ellas. | Señala membrana, citoplasma y núcleo en preparaciones al microscopio o en imágenes y describe la función de cada uno. | Predice y comprueba con un experimento sencillo (papa o huevo en agua con sal) el paso de agua y sustancias a través de una membrana.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>La célula como unidad de la vida, Niveles de organización de los seres vivos</t>
+          <t>La célula como unidad de la vida, Niveles de organización de los seres vivos, Biomoléculas, Estructuras celulares básicas, Membrana celular, Difusión y ósmosis</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>CO 4, SG 5, UY 4 (La célula como unidad de la vida); T8_27-B2.1 Estructura y funciones de la célula</t>
+          <t>CO 4, SG 5, UY 4 (La célula como unidad de la vida); prerrequisito: Difusión y ósmosis (bloqueo de Transporte en plantas, ENG 2, SG 5, UY 3, y de Intercambio de gases en animales, ENG 6, SG 5, UY 5); prerrequisito: Membrana celular ← Biomoléculas y Estructuras celulares básicas (confianza alta); T8_27-B2.1 Estructura y funciones de la célula</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Los tres países presentan la célula como unidad de la vida en 4.° o 5.°. Los niveles de organización se trasladan con ella porque son la base de los sistemas del cuerpo que llegan a 5.°.</t>
+          <t>Los países presentan la célula en 4.° o 5.°. La difusión, bloqueo del transporte y del intercambio de gases, llega con lo que necesita: niveles de organización, biomoléculas y partes básicas de la célula, en nivel experimental.</t>
         </is>
       </c>
     </row>
@@ -592,16 +592,16 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>G06-CIE-U5-5.1, G06-CIE-U5-5.9</t>
+          <t>G06-CIE-U5-5.1</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>6</v>
@@ -616,27 +616,27 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>7.3. Identificación experimental de los grupos de biomoléculas en los alimentos y del carbono como su elemento base. | 7.4. Identificación de las estructuras básicas de la célula: membrana, citoplasma (citosol) y núcleo.</t>
+          <t>7.3. Identificación experimental de los grupos de biomoléculas en los alimentos y del carbono como su elemento base.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Identifica con pruebas sencillas (yodo, papel, Biuret) almidón, grasas y proteínas en alimentos y reconoce el carbono como elemento común a todas ellas. | Señala membrana, citoplasma y núcleo en preparaciones al microscopio o en imágenes y describe la función de cada uno.</t>
+          <t>Identifica con pruebas sencillas almidón, grasas y proteínas en alimentos y reconoce el carbono como elemento común a todas ellas.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Biomoléculas, El carbono y las moléculas orgánicas, Estructuras celulares básicas</t>
+          <t>Biomoléculas, El carbono y las moléculas orgánicas</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Biomoléculas y Estructuras celulares básicas (confianza alta) de Membrana celular, que llega a 5.° con la difusión; prerrequisito: El carbono y las moléculas orgánicas (hoy en 11.°) de Biomoléculas, confianza alta; SG 5 (La célula como unidad de la vida)</t>
+          <t>prerrequisito: El carbono y las moléculas orgánicas (hoy en 11.°) de Biomoléculas, confianza alta</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>La membrana, necesaria para la difusión, depende de biomoléculas y estructuras celulares. Se adelantan a nivel básico: pruebas de alimentos y partes de la célula. El tema 5.1 incorpora el carbono y corrige la secuencia carbono → biomoléculas.</t>
+          <t>Complementa la acción 1: el tema de biomoléculas, ya trasladado a 5.°, incorpora el carbono como base de las moléculas orgánicas y corrige una secuencia invertida de seis grados sin gastar presupuesto.</t>
         </is>
       </c>
     </row>
@@ -651,46 +651,46 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U5-5.8</t>
+          <t>G08-CIE-U6-6.2, G08-CIE-U6-6.4, G08-CIE-U6-6.5</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>5</v>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7. La célula y la organización de los seres vivos</t>
+          <t>7. Estructura y transporte en las plantas (nueva en 6.°, después de 5.7 y 6.2)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7.5. Demostración experimental de la difusión y la ósmosis a través de la membrana celular.</t>
+          <t>7.1. Identificación práctica de los tejidos de conducción y sostén en raíz, tallo y hoja. | 7.2. Explicación del transporte de agua y nutrientes en las plantas. | 7.3. Exploración de las estructuras vegetales que conducen y almacenan sustancias.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Predice y comprueba con un experimento sencillo (papa o huevo en agua con sal) el paso de agua y sustancias a través de una membrana.</t>
+          <t>Señala en cortes de raíz, tallo y hoja dónde están los vasos conductores. | Demuestra con un tallo en agua coloreada el recorrido del agua desde la raíz hasta las hojas y lo explica con un esquema. | Distingue órganos de conducción y de almacenamiento (tubérculos, raíces, semillas) en plantas de su entorno.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Difusión y ósmosis, Membrana celular</t>
+          <t>Tejidos vegetales, Transporte en plantas: xilema y floema</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Difusión y ósmosis (bloqueo de Transporte en plantas, SG 5, UY 3); prerrequisito: Difusión y ósmosis (bloqueo de Intercambio de gases en animales, SG 5, UY 5); prerrequisito: Membrana celular ← Biomoléculas y Estructuras celulares básicas (acción 2)</t>
+          <t>ENG 2, SG 5, UY 3 (Transporte en plantas: xilema y floema); prerrequisito: Tejidos vegetales ← Diferenciación y especialización celular ← Mitosis y ciclo celular ← ADN y cromosomas (confianza alta, todos en 6.°); prerrequisito: Difusión y ósmosis (5.°, acción 1)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Es el bloqueo común del transporte en plantas y del intercambio de gases. Se trabaja de forma experimental y cualitativa, después de las biomoléculas y las partes de la célula (acción 2).</t>
+          <t>Inglaterra, Singapur y Uruguay lo enseñan entre 2.° y 5.°; El Salvador, en 8.°. Sube a 6.°, no a 5.°, porque los tejidos requieren diferenciación celular y mitosis, que están en 6.°.</t>
         </is>
       </c>
     </row>
@@ -705,46 +705,48 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U6-6.2, G08-CIE-U6-6.4, G08-CIE-U6-6.5</t>
+          <t>G06-CIE-U6-6.9, G08-CIE-U6-6.7</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>6 y 8</t>
+        </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>7. Estructura y transporte en las plantas (nueva en 6.°, después de 5.7 y 6.2)</t>
+          <t>8. Funciones vitales de plantas y animales</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>7.1. Identificación práctica de los tejidos de conducción y sostén en raíz, tallo y hoja. | 7.2. Explicación del transporte de agua y nutrientes en las plantas. | 7.3. Exploración de las estructuras vegetales que conducen y almacenan sustancias.</t>
+          <t>8.1. Práctica con técnicas de propagación vegetal asexual. | 8.3. Experimentación con las condiciones de germinación y crecimiento de las plantas.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Señala en cortes de raíz, tallo y hoja dónde están los vasos conductores. | Demuestra con un tallo en agua coloreada el recorrido del agua desde la raíz hasta las hojas y lo explica con un esquema. | Distingue órganos de conducción y de almacenamiento (tubérculos, raíces, semillas) en plantas de su entorno.</t>
+          <t>Propaga una planta por esqueje, estolón o tubérculo y compara la descendencia obtenida con la reproducción por semillas. | Diseña un ensayo con una sola variable (agua, luz o temperatura) y registra en una tabla la germinación y el crecimiento de semillas.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Tejidos vegetales, Transporte en plantas: xilema y floema</t>
+          <t>Reproducción sexual y asexual, Biotecnología vegetal y agroindustria, Ciclo de vida de las plantas, Necesidades de los seres vivos</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>SG 5, UY 3 (Transporte en plantas: xilema y floema); prerrequisito: Tejidos vegetales ← Diferenciación y especialización celular ← Mitosis y ciclo celular ← ADN y cromosomas (confianza alta, todos en 6.°); prerrequisito: Difusión y ósmosis (5.°, acción 3)</t>
+          <t>prerrequisito: Reproducción sexual y asexual (bloqueo de Reproducción sexual de las plantas con flor: ENG 2, UY 3, SG 5, AU 8)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Los países lo enseñan en 3.° a 5.°; El Salvador, en 8.°. Sube a 6.°, no a 5.°, porque los tejidos requieren diferenciación celular y mitosis, que están en 6.°. Va después de ellas.</t>
+          <t>La propagación asexual introduce el bloqueo de la reproducción de plantas con flor; la germinación cierra el ciclo de la planta. Ambos son prácticas concretas, apropiadas para 5.°, sin prerrequisitos tardíos.</t>
         </is>
       </c>
     </row>
@@ -754,12 +756,12 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>dividir</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>G06-CIE-U6-6.9</t>
+          <t>G06-CIE-U6-6.8</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -773,32 +775,32 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8. Funciones vitales de plantas y animales</t>
+          <t>8. Funciones vitales de plantas y animales (5.°); la parte de división celular queda en 6. Biología del desarrollo (6.°)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8.1. Práctica con técnicas de propagación vegetal asexual.</t>
+          <t>8.2. Descripción de la polinización, la fecundación y la formación de semillas y frutos en las plantas con flor. | 6.8. Descripción de los planos de división celular en el desarrollo de las plantas (se mantiene en 6.°, con sus conceptos).</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Propaga una planta por esqueje, estolón o tubérculo y compara la descendencia obtenida con la reproducción por semillas.</t>
+          <t>Identifica en una flor real las partes que intervienen en la polinización y la fecundación y relaciona el ovario con el fruto y el óvulo con la semilla. | Relaciona los planos de división celular con el crecimiento y la forma de los órganos vegetales.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual, Biotecnología vegetal y agroindustria</t>
+          <t>Reproducción sexual de las plantas con flor</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Reproducción sexual y asexual (bloqueo de Reproducción sexual de las plantas con flor, SG 5, UY 3)</t>
+          <t>ENG 2, UY 3, SG 5, AU 8 (Reproducción sexual de las plantas con flor); prerrequisito: Reproducción sexual y asexual (acción 4)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Introduce en 5.° la distinción entre reproducción sexual y asexual, que es el bloqueo de la reproducción de plantas con flor. Es una práctica concreta y apropiada para la edad.</t>
+          <t>El tema mezcla fecundación de plantas con flor (países: 3.° a 5.°) y división celular (requiere mitosis, 6.°). Se separan: solo la fecundación baja a 5.°; la mitosis no se adelanta.</t>
         </is>
       </c>
     </row>
@@ -808,51 +810,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>dividir</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>G06-CIE-U6-6.8</t>
+          <t>G08-CIE-U7-7.9, G08-CIE-U7-7.7, G08-CIE-U7-7.8, G08-CIE-U7-7.10</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>8. Funciones vitales de plantas y animales (5.°); la parte de división celular queda en 6. Biología del desarrollo (6.°)</t>
+          <t>8. Funciones vitales de plantas y animales</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>8.2. Descripción de la polinización, la fecundación y la formación de semillas y frutos en las plantas con flor. | 6.8. Descripción de los planos de división celular en el desarrollo de las plantas (se mantiene en 6.°, con sus conceptos).</t>
+          <t>8.4. Modelaje de una estructura respiratoria. | 8.5. Demostración práctica del vínculo entre el intercambio de gases y la circulación. | 8.6. Reconocimiento de las estructuras respiratorias y circulatorias del ser humano y de otros vertebrados. | 8.7. Exploración de la estructura y las funciones del sistema digestivo humano.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Identifica en una flor real las partes que intervienen en la polinización y la fecundación y relaciona el ovario con el fruto y el óvulo con la semilla. | Relaciona los planos de división celular con el crecimiento y la forma de los órganos vegetales.</t>
+          <t>Construye un modelo de pulmón (botella y globos) y explica la entrada y salida de aire. | Explica con un esquema cómo la sangre lleva el oxígeno de los pulmones a las células y el dióxido de carbono de vuelta. | Compara con imágenes o modelos pulmones, branquias y corazón en peces, aves y mamíferos. | Ubica en un modelo los órganos del sistema digestivo y describe qué ocurre con el alimento en cada uno.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Reproducción sexual de las plantas con flor</t>
+          <t>Intercambio de gases en animales, Sistema respiratorio, Sistema circulatorio, Sistema digestivo</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>SG 5, UY 3 (Reproducción sexual de las plantas con flor); prerrequisito: Reproducción sexual y asexual (acción 5)</t>
+          <t>ENG 6, SG 5, UY 5 (Intercambio de gases en animales); ENG 4, SG 4, UY 4 (Digestión química y absorción de nutrientes); prerrequisito: Difusión y ósmosis (acción 1)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>El tema mezcla fecundación de plantas con flor (países: 3.° a 5.°) y división celular (requiere mitosis, 6.°). Se separan: solo la fecundación baja a 5.°; la mitosis no se adelanta.</t>
+          <t>Los países de alto desempeño enseñan respiración, circulación y digestión entre 4.° y 6.°; El Salvador, en 8.°. Se adelantan los sistemas; su único bloqueo, la difusión, llega a 5.° en la acción 1.</t>
         </is>
       </c>
     </row>
@@ -867,46 +869,46 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U6-6.7</t>
+          <t>G07-CIE-U4-4.1, G07-CIE-U4-4.2, G07-CIE-U4-4.5</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>5</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8. Funciones vitales de plantas y animales</t>
+          <t>9. Interacciones en los ecosistemas</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8.3. Experimentación con las condiciones de germinación y crecimiento de las plantas.</t>
+          <t>9.1. Identificación de interacciones ecológicas a partir de contextos prácticos. | 9.2. Descripción de interacciones ecológicas observadas en contextos prácticos. | 9.3. Identificación de productores, consumidores y descomponedores en las redes tróficas de un ecosistema local.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Diseña un ensayo con una sola variable (agua, luz o temperatura) y registra en una tabla la germinación y el crecimiento de semillas.</t>
+          <t>Clasifica ejemplos locales como competencia, depredación, mutualismo, comensalismo o parasitismo. | Describe una interacción observada (en la escuela o en un video) indicando qué gana o pierde cada especie. | Construye una red trófica de un ecosistema local y explica qué pasaría si desapareciera una especie.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Ciclo de vida de las plantas, Necesidades de los seres vivos</t>
+          <t>Competencia por recursos, Depredación, Relaciones intraespecíficas, Simbiosis: mutualismo, comensalismo y parasitismo, Productores, consumidores y descomponedores, Redes tróficas</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>SG 5, UY 3 (Reproducción sexual de las plantas con flor: de la semilla a la nueva planta)</t>
+          <t>CO 3, ENG 6 (Competencia por recursos); CO 3, ENG 2 (Depredación); CO 3, UY 6 (Relaciones intraespecíficas); prerrequisito: Competencia por recursos (bloqueo, se mueve en 4.1)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Cierra en 5.° el ciclo de la planta con flor (flor, semilla, germinación) que los países enseñan en primaria. No depende de contenidos de 8.° y aporta una investigación sencilla.</t>
+          <t>Colombia e Inglaterra introducen competencia y depredación entre 2.° y 6.°. 4.1 y 4.2 se mueven juntos para que la competencia (bloqueo) llegue con la simbiosis; 4.5 prepara el flujo de energía.</t>
         </is>
       </c>
     </row>
@@ -916,51 +918,51 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U7-7.9, G08-CIE-U7-7.7, G08-CIE-U7-7.8</t>
+          <t>G08-CIE-U6-6.10, G08-CIE-U6-6.12</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>8</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>8. Funciones vitales de plantas y animales</t>
+          <t>5. Célula. (después de 5.12 y 5.17)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>8.4. Modelaje de una estructura respiratoria. | 8.5. Demostración práctica del vínculo entre el intercambio de gases y la circulación. | 8.6. Reconocimiento de las estructuras respiratorias y circulatorias del ser humano y de otros vertebrados.</t>
+          <t>5.23. Indagación del intercambio de gases en las hojas y su relación con la fotosíntesis y la respiración.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Construye un modelo de pulmón (botella y globos) y explica la entrada y salida de aire. | Explica con un esquema cómo la sangre lleva el oxígeno de los pulmones a las células y el dióxido de carbono de vuelta. | Compara con imágenes o modelos pulmones, branquias y corazón en peces, aves y mamíferos.</t>
+          <t>Explica, con evidencias de un experimento con hojas, qué gases entran y salen de día y de noche y lo relaciona con la fotosíntesis y la respiración.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Intercambio de gases en animales, Sistema respiratorio, Sistema circulatorio</t>
+          <t>Intercambio de gases en plantas, Fotosíntesis, Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>SG 5, UY 5 (Intercambio de gases en animales); prerrequisito: Difusión y ósmosis (acción 3)</t>
+          <t>ENG 6, SG 5, UY 5 (Intercambio de gases en plantas); prerrequisito: Fotosíntesis y Respiración celular (6.°); prerrequisito: Difusión y ósmosis (acción 1)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>Singapur y Uruguay lo enseñan en 5.°; El Salvador, en 8.°. Su bloqueo, la difusión, pasa a 5.° (acción 3). Se suma 7.8 para mantener 5.° sobre el 15 %.</t>
+          <t>6.10 y 6.12 trabajan las funciones de la hoja. Unidas suben a 6.°, el primer grado posible tras fotosíntesis y respiración. Libera el tema que necesita la división de G06-6.8 (acción 5).</t>
         </is>
       </c>
     </row>
@@ -970,51 +972,51 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U7-7.10</t>
+          <t>G06-CIE-U5-5.19, G06-CIE-U5-5.20</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>8. Funciones vitales de plantas y animales</t>
+          <t>5. Célula.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8.7. Exploración de la estructura y las funciones del sistema digestivo humano.</t>
+          <t>5.19. Descripción de la estructura y las funciones de la matriz extracelular en los tejidos.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Ubica en un modelo los órganos del sistema digestivo y describe qué ocurre con el alimento en cada uno.</t>
+          <t>Describe la composición de la matriz extracelular y explica su función en un tejido observado al microscopio.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Sistema digestivo</t>
+          <t>Diferenciación y especialización celular</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>SG 4, UY 4 (Digestión química y absorción de nutrientes); prerrequisito: Enzimas (8.°) impide adelantar 7.11</t>
+          <t>fusión: ambos temas trabajan Diferenciación y especialización celular (matriz extracelular)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Los países enseñan la digestión en 4.°. Se adelanta solo la parte estructural; la digestión química (7.11) queda en 8.° porque depende de enzimas, que El Salvador enseña en 8.°.</t>
+          <t>Descripción y observación de la matriz extracelular son dos caras del mismo contenido. La fusión libera un tema para pagar la célula animal y vegetal (acción 10).</t>
         </is>
       </c>
     </row>
@@ -1024,51 +1026,45 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>G07-CIE-U4-4.1, G07-CIE-U4-4.2, G07-CIE-U4-4.5</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr"/>
       <c r="D11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>9. Interacciones en los ecosistemas</t>
+          <t>5. Célula.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>9.1. Identificación de interacciones ecológicas a partir de contextos prácticos. | 9.2. Descripción de interacciones ecológicas observadas en contextos prácticos. | 9.3. Identificación de productores, consumidores y descomponedores en las redes tróficas de un ecosistema local.</t>
+          <t>5.24. Comparación de la célula animal y la célula vegetal mediante observación al microscopio.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Clasifica ejemplos locales como competencia, depredación, mutualismo, comensalismo o parasitismo. | Describe una interacción observada (en la escuela o en un video) indicando qué gana o pierde cada especie. | Construye una red trófica de un ecosistema local y explica qué pasaría si desapareciera una especie.</t>
+          <t>Elabora un cuadro comparativo de pared celular, cloroplastos y vacuola a partir de sus propias preparaciones de epidermis de cebolla y mucosa bucal.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Competencia por recursos, Depredación, Relaciones intraespecíficas, Simbiosis: mutualismo, comensalismo y parasitismo, Productores, consumidores y descomponedores, Redes tróficas</t>
+          <t>Célula animal y célula vegetal</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>CO 3, UY 6 (Simbiosis; Relaciones intraespecíficas); prerrequisito: Competencia por recursos (bloqueo, se mueve en 4.1); T8_27-B5.2 Flujo de energía en los ecosistemas (reforzar)</t>
+          <t>AU 7, CO 6,5, ENG 6, UY 7 (Célula animal y célula vegetal); prerrequisito: Estructuras celulares básicas (5.°, acción 1); T8_27-B2.1 Estructura y funciones de la célula</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Colombia introduce las interacciones en 3.°. Se mueven 4.1 y 4.2 juntos para que la competencia (bloqueo) llegue con ellas, y 4.5 deja las redes tróficas listas para el flujo de energía.</t>
+          <t>Hoy solo aparece en 11.° (G11-BIO-U3-3.3). Inglaterra lo enseña en 6.° y Australia y Uruguay en 7.°. Va en 6.° después de las partes básicas de la célula. Se paga con la fusión 9.</t>
         </is>
       </c>
     </row>
@@ -1083,46 +1079,46 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>G08-CIE-U6-6.10, G08-CIE-U6-6.12</t>
+          <t>G07-CIE-U2-2.5, G07-CIE-U2-2.6</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5. Célula. (después de 5.12 y 5.17)</t>
+          <t>2. Genética y evolución</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5.23. Indagación del intercambio de gases en las hojas y su relación con la fotosíntesis y la respiración.</t>
+          <t>2.5. Simulación y explicación del proceso de replicación del ADN.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Explica, con evidencias de un experimento con hojas, qué gases entran y salen de día y de noche y lo relaciona con la fotosíntesis y la respiración.</t>
+          <t>Simula con un modelo la replicación del ADN y la explica con un recurso propio (esquema, video o maqueta).</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Intercambio de gases en plantas, Fotosíntesis, Partes de la planta y sus funciones</t>
+          <t>Estructura del ADN, Replicación del ADN</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>SG 5, UY 5 (Intercambio de gases en plantas); prerrequisito: Fotosíntesis y Respiración celular (6.°); prerrequisito: Difusión y ósmosis (acción 3)</t>
+          <t>fusión: ambos temas trabajan Replicación del ADN (2.4 también lo trabaja)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6.10 y 6.12 trabajan las funciones de la hoja. Unidas suben a 6.°, el primer grado posible tras fotosíntesis y respiración. Libera el tema que necesita la división de G06-6.8 (acción 6).</t>
+          <t>La malla dedica tres temas a la replicación del ADN (2.4, 2.5 y 2.6). Unir simulación y elaboración de recursos libera un tema para la acción 12.</t>
         </is>
       </c>
     </row>
@@ -1132,51 +1128,45 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>G06-CIE-U5-5.19, G06-CIE-U5-5.20</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr"/>
       <c r="D13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>5. Célula.</t>
+          <t>4. Ecología (después de trabajar el ciclo del agua)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>5.19. Descripción de la estructura y las funciones de la matriz extracelular en los tejidos.</t>
+          <t>4.13. Explicación del papel de los seres vivos en los ciclos del agua, del oxígeno y del carbono.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Describe la composición de la matriz extracelular y explica su función en un tejido observado al microscopio.</t>
+          <t>Representa en un esquema cómo la fotosíntesis, la respiración, la transpiración y la descomposición mueven agua, oxígeno y carbono en un ecosistema local.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Diferenciación y especialización celular</t>
+          <t>Papel de los seres vivos en el ciclo del agua, Ciclos del carbono y del oxígeno</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Diferenciación y especialización celular (matriz extracelular)</t>
+          <t>CO 6,5, SG 5 (Papel de los seres vivos en el ciclo del agua); CO 6,5, ENG 6 (Ciclos del carbono y del oxígeno); T8_27-B5.3 Ciclos del agua, el oxígeno y el carbono (reforzar: 1 tema, débil); prerrequisito: Ciclo del agua (7.°); Fotosíntesis y Respiración celular (6.°)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Descripción y observación de la matriz extracelular son dos caras del mismo contenido. La fusión libera un tema para pagar la célula animal y vegetal (acción 13).</t>
+          <t>B5.3 tiene un solo tema débil. Los ciclos del carbono y del oxígeno podrían ir en 6.°, pero el del agua llega en 7.°; se tratan juntos en 7.°, tras ese tema. Se paga con la fusión 11.</t>
         </is>
       </c>
     </row>
@@ -1186,45 +1176,51 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>G07-CIE-U4-4.8</t>
+        </is>
+      </c>
       <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="F14" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5. Célula.</t>
+          <t>5. Célula. (después de fotosíntesis y respiración; o unidad nueva «Energía en los ecosistemas»)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5.24. Comparación de la célula animal y la célula vegetal mediante observación al microscopio.</t>
+          <t>5.25. Reconocimiento de la estructura de los ecosistemas y construcción de pirámides ecológicas para explicar el flujo de energía.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Elabora un cuadro comparativo de pared celular, cloroplastos y vacuola a partir de sus propias preparaciones de epidermis de cebolla y mucosa bucal.</t>
+          <t>Construye una pirámide de energía con datos de un ecosistema local y explica por qué hay menos energía disponible en cada nivel trófico.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Célula animal y célula vegetal</t>
+          <t>Factores bióticos y abióticos, Flujo de energía y pirámides ecológicas, Productores, consumidores y descomponedores</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>CO 6, UY 7 (Célula animal y célula vegetal); prerrequisito: Estructuras celulares básicas (5.°, acción 2); T8_27-B2.1 Estructura y funciones de la célula</t>
+          <t>AU 6, CO 6,5, SG 6, UY 6 (Flujo de energía y pirámides ecológicas); T8_27-B5.2 Flujo de energía en los ecosistemas (reforzar: 1 tema, débil); prerrequisito: Redes tróficas (5.°, acción 7)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Hoy solo aparece en 11.° (G11-BIO-U3-3.3). Colombia lo enseña en 6.°. Va en 6.° después de las estructuras celulares básicas. Se paga con la fusión 12.</t>
+          <t>Australia, Singapur y Uruguay enseñan el flujo de energía en 6.°; El Salvador, en 7.° (débil) y 10.°. Sube a 6.° reformulado con pirámides, tras las redes tróficas de 5.° y la fotosíntesis de 6.°.</t>
         </is>
       </c>
     </row>
@@ -1234,51 +1230,51 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>G07-CIE-U2-2.5, G07-CIE-U2-2.6</t>
+          <t>G06-CIE-U5-5.2</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2. Genética y evolución</t>
+          <t>5. Célula.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>2.5. Simulación y explicación del proceso de replicación del ADN.</t>
+          <t>5.2. Experimentación con la actividad de las enzimas como proteínas formadas por cadenas de aminoácidos.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Simula con un modelo la replicación del ADN y la explica con un recurso propio (esquema, video o maqueta).</t>
+          <t>Comprueba el efecto de una enzima (por ejemplo, la catalasa de la papa) en distintas condiciones y explica que su función depende de su estructura de proteína.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Estructura del ADN, Replicación del ADN</t>
+          <t>Enzimas, Catalizadores, Proteínas: estructura y función, Aminoácidos y estructura de las proteínas</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Replicación del ADN (2.4 también lo trabaja)</t>
+          <t>prerrequisito: Proteínas: estructura y función (hoy en 10.°) de Enzimas (6.°), confianza alta; prerrequisito: Aminoácidos y estructura de las proteínas (hoy en 11.°) de Proteínas, confianza alta</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>La malla dedica tres temas a la replicación del ADN (2.4, 2.5 y 2.6). Unir simulación y elaboración de recursos libera un tema para la acción 15.</t>
+          <t>Las enzimas llegan en 6.° antes que las proteínas (10.°). El tema se reformula para presentarlas como proteínas formadas por aminoácidos, sin gastar presupuesto. Prepara la digestión química (acción 15).</t>
         </is>
       </c>
     </row>
@@ -1288,45 +1284,51 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>G08-CIE-U7-7.11</t>
+        </is>
+      </c>
       <c r="D16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>8</v>
+      </c>
       <c r="F16" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4. Ecología (después de trabajar el ciclo del agua)</t>
+          <t>5. Célula. (después de 5.2)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4.13. Explicación del papel de los seres vivos en los ciclos del agua, del oxígeno y del carbono.</t>
+          <t>5.26. Experimentación con los procesos químicos y mecánicos que intervienen en la digestión.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Representa en un esquema cómo la fotosíntesis, la respiración, la transpiración y la descomposición mueven agua, oxígeno y carbono en un ecosistema local.</t>
+          <t>Comprueba con un experimento (amilasa de la saliva y almidón) la acción de una enzima digestiva y la distingue de la digestión mecánica.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Papel de los seres vivos en el ciclo del agua</t>
+          <t>Digestión química y absorción de nutrientes, Enzimas, Sistema digestivo</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>CO 6, SG 5 (Papel de los seres vivos en el ciclo del agua); T8_27-B5.3 Ciclos del agua, el oxígeno y el carbono (reforzar: 1 tema, débil); prerrequisito: Ciclo del agua (7.°)</t>
+          <t>ENG 4, SG 4, UY 4 (Digestión química y absorción de nutrientes); prerrequisito: Enzimas (6.°, acción 14); prerrequisito: Sistema digestivo (5.°, acción 6)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>El objetivo B5.3 tiene un solo tema débil en el ciclo. No puede ir en 6.° porque el ciclo del agua llega en 7.°; se ubica en 7.° después de él. Se paga con la fusión 14.</t>
+          <t>Inglaterra, Singapur y Uruguay la enseñan en 4.°; El Salvador, en 8.°. Su bloqueo, las enzimas, ahora está en 6.° (G06-5.2), así que sube a 6.° justo después de ese tema.</t>
         </is>
       </c>
     </row>
@@ -1336,51 +1338,51 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>G07-CIE-U4-4.8</t>
+          <t>G08-CIE-U7-7.13, G08-CIE-U7-7.15</t>
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>4. Ecología</t>
+          <t>7. Anatomía y Fisiología Animal</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>4.8. Reconocimiento de la estructura de los ecosistemas y construcción de pirámides ecológicas para explicar el flujo de energía.</t>
+          <t>7.13. Indagación de los procesos y mecanismos de excreción en los animales.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Construye una pirámide de energía con datos de un ecosistema local y explica por qué hay menos energía disponible en cada nivel trófico.</t>
+          <t>Compara los mecanismos de excreción de distintos grupos de animales y los relaciona con el ambiente en que viven.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Factores bióticos y abióticos, Flujo de energía y pirámides ecológicas, Productores, consumidores y descomponedores</t>
+          <t>Osmorregulación y equilibrio hídrico, Sistema excretor</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>CO 6, SG 6, UY 6 (Flujo de energía y pirámides ecológicas); T8_27-B5.2 Flujo de energía en los ecosistemas (reforzar: 1 tema, débil)</t>
+          <t>fusión: ambos temas trabajan Sistema excretor y Osmorregulación (7.14 también)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Se reformula para trabajar explícitamente las pirámides de energía, hoy solo en 10.°. Queda en 7.° por coherencia con la unidad; el MINED puede valorar pasarlo a 6.°, como los tres países.</t>
+          <t>La excreción ocupa tres temas (7.13, 7.14 y 7.15). Unir procesos generales y mecanismos libera un tema para la homeostasis (acción 17).</t>
         </is>
       </c>
     </row>
@@ -1390,51 +1392,45 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>G08-CIE-U7-7.11</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n">
         <v>8</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7. Anatomía y Fisiología Animal</t>
+          <t>7. Anatomía y Fisiología Animal (después de excreción)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7.11. Experimentación con los procesos químicos y mecánicos de la digestión y con la acción de las enzimas, proteínas formadas por cadenas de aminoácidos.</t>
+          <t>7.16. Explicación de la homeostasis y de la regulación hormonal del medio interno.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Comprueba el efecto de una enzima digestiva (por ejemplo, la amilasa de la saliva) y explica que su función depende de su estructura de proteína.</t>
+          <t>Explica con un ejemplo (glucosa en sangre o temperatura corporal) cómo los sistemas excretor y endocrino mantienen el equilibrio interno, e identifica las glándulas que intervienen.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Digestión química y absorción de nutrientes, Enzimas, Proteínas: estructura y función, Aminoácidos y estructura de las proteínas, Sistema digestivo</t>
+          <t>Homeostasis, Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>prerrequisito: Proteínas: estructura y función (hoy en 10.°) de Enzimas (8.°), confianza alta; SG 4, UY 4 (Digestión química y absorción de nutrientes); prerrequisito: Aminoácidos y estructura de las proteínas (hoy en 11.°) de Proteínas, confianza alta</t>
+          <t>CO 8, UY 8 (Homeostasis); AU 8, CO 8, UY 8 (Sistema endocrino y hormonas); prerrequisito: Homeostasis (bloqueo del sistema endocrino, se introduce primero en el mismo tema)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Depende de enzimas, así que no baja a 5.°. Se reformula en 8.° para presentar las enzimas como proteínas formadas por aminoácidos y corregir la secuencia aminoácidos → proteínas → enzimas.</t>
+          <t>Australia, Colombia y Uruguay enseñan hormonas en 8.°; El Salvador, en 10.°. Un tema introductorio en 8.°, tras la excreción, resuelve el bloqueo de homeostasis. Se paga con la fusión 16.</t>
         </is>
       </c>
     </row>
@@ -1444,51 +1440,45 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>G08-CIE-U7-7.13, G08-CIE-U7-7.15</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr"/>
       <c r="D19" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>7. Anatomía y Fisiología Animal</t>
+          <t>6. Ciencias de la Tierra. (se inserta antes del actual 6.5, que pasa a 6.6)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>7.13. Indagación de los procesos y mecanismos de excreción en los animales.</t>
+          <t>6.5. Explicación de la formación de los fósiles y del registro fósil como evidencia de los cambios de los seres vivos.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Compara los mecanismos de excreción de distintos grupos de animales y los relaciona con el ambiente en que viven.</t>
+          <t>Modela la formación de un fósil y explica, con ejemplos de fósiles de El Salvador o de la región, qué muestran sobre los seres vivos del pasado y sus cambios.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Osmorregulación y equilibrio hídrico, Sistema excretor</t>
+          <t>Fósiles y registro fósil, Evidencias de la evolución</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Sistema excretor y Osmorregulación (7.14 también)</t>
+          <t>CO 2, ENG 4 (Fósiles y registro fósil); AU 9, CO 2, ENG 4 (Evidencias de la evolución); prerrequisito: Fósiles y registro fósil (hoy en 10.°) de Historia de la vida en la Tierra (5.°, G05-6.5), confianza alta; prerrequisito: Evidencias de la evolución de Filogenia (7.°), confianza alta</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>La excreción ocupa tres temas (7.13, 7.14 y 7.15). Unir procesos generales y mecanismos libera un tema para la homeostasis (acción 19).</t>
+          <t>El tema de fósiles de 5.° pasó a Ciencias de la Tierra, y Biología quedó sin fósiles antes de 10.°. Inglaterra los enseña en 4.°. Corrige dos secuencias: historia de la vida y filogenia. Se paga con la fusión 19.</t>
         </is>
       </c>
     </row>
@@ -1498,45 +1488,51 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr"/>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>G07-CIE-U2-2.2, G07-CIE-U2-2.3</t>
+        </is>
+      </c>
       <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="F20" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7. Anatomía y Fisiología Animal (después de excreción)</t>
+          <t>2. Genética y evolución</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7.16. Explicación de la homeostasis y de la regulación hormonal del medio interno.</t>
+          <t>2.2. Experimentación con técnicas de extracción y tinción de ácidos nucleicos y explicación de su funcionamiento.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Explica con un ejemplo (glucosa en sangre o temperatura corporal) cómo los sistemas excretor y endocrino mantienen el equilibrio interno, e identifica las glándulas que intervienen.</t>
+          <t>Extrae ADN de un vegetal con materiales caseros y explica qué hace cada paso del procedimiento.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Homeostasis, Sistema endocrino y hormonas</t>
+          <t>ADN y cromosomas, Membrana celular</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>CO 8, UY 8 (Homeostasis); CO 8, UY 8 (Sistema endocrino y hormonas); prerrequisito: Homeostasis (bloqueo del sistema endocrino, se introduce primero en el mismo tema)</t>
+          <t>fusión: ambos temas trabajan ADN y cromosomas (extracción y tinción de ácidos nucleicos)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>Colombia y Uruguay enseñan homeostasis y hormonas en 8.°; El Salvador, en 10.°. Un tema introductorio en 8.°, tras la excreción, resuelve el bloqueo. Se paga con la fusión 18.</t>
+          <t>La práctica de extracción y su explicación son el mismo contenido en dos temas consecutivos. Unirlos libera un tema para los fósiles de 5.° (acción 18) y alivia 7.°, el grado más cargado.</t>
         </is>
       </c>
     </row>
@@ -1551,46 +1547,46 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>G05-CIE-U6-6.3</t>
+          <t>G07-CIE-U2-2.8</t>
         </is>
       </c>
       <c r="D21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>6. Ciencias de la Tierra.</t>
+          <t>2. Genética y evolución</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>6.3. Explicación del registro fósil, de su datación y de su valor como evidencia de la evolución.</t>
+          <t>2.8. Visualización de polimorfismos y de la variación genética en la descendencia a partir de casos.</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Ordena fósiles o imágenes de fósiles por su antigüedad y explica qué cambios de los seres vivos a lo largo del tiempo muestran.</t>
+          <t>Explica con casos (familias, cruces o semillas) por qué los descendientes de los mismos progenitores son distintos entre sí.</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>Fósiles y registro fósil, Evidencias de la evolución</t>
+          <t>Genes y alelos, Variación genética en la descendencia</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Evidencias de la evolución (hoy en 10.°) de Filogenia y parentesco evolutivo (7.°), confianza alta</t>
+          <t>prerrequisito: Variación genética en la descendencia (hoy en 11.°) de Selección natural (7.°), confianza alta; CO 8,5, ENG 4 (Variación genética en la descendencia)</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>Corrige sin gastar presupuesto una secuencia invertida de 3 grados: el tema de fósiles de 5.° ya existe y se reformula para presentarlos como evidencia de la evolución antes de la cladística de 7.°.</t>
+          <t>La selección natural (2.15) necesita la variación en la descendencia, que el grafo ubica en 11.°. Se hace explícita en 2.8, que ya está en 7.° antes de 2.15, sin gastar presupuesto.</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1649,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
         <v>17</v>
@@ -1676,10 +1672,10 @@
         <v>6</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1699,10 +1695,10 @@
         <v>7</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>
@@ -1725,7 +1721,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="4">
         <f>C5-B5</f>

--- a/asignaturas/biologia/propuesta/Propuesta_Biologia_G05-G08.xlsx
+++ b/asignaturas/biologia/propuesta/Propuesta_Biologia_G05-G08.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>7.1. Construcción de una línea temporal sobre el desarrollo de la teoría celular. | 7.2. Representación de los niveles de organización de los seres vivos, de la célula al organismo. | 7.3. Identificación experimental de los grupos de biomoléculas en los alimentos y del carbono como su elemento base. | 7.4. Identificación de las estructuras básicas de la célula: membrana, citoplasma (citosol) y núcleo. | 7.5. Demostración experimental de la difusión y la ósmosis a través de la membrana celular.</t>
+          <t>7.1. Construcción de una línea temporal sobre el desarrollo de la teoría celular. | 7.2. Representación de los niveles de organización de los seres vivos, de la célula al organismo. | 7.3. Identificación experimental de los grupos de biomoléculas en los alimentos y del carbono como su elemento base. | 7.5. Identificación de las estructuras básicas de la célula: membrana, citoplasma (citosol) y núcleo. | 7.6. Demostración experimental de la difusión y la ósmosis a través de la membrana celular.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>La célula como unidad de la vida, Niveles de organización de los seres vivos, Biomoléculas, Estructuras celulares básicas, Membrana celular, Difusión y ósmosis</t>
+          <t>La célula como unidad de la vida, Niveles de organización de los seres vivos, Biomoléculas, El carbono y las moléculas orgánicas, Estructuras celulares básicas, Membrana celular, Difusión y ósmosis</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>CO 4, SG 5, UY 4 (La célula como unidad de la vida); prerrequisito: Difusión y ósmosis (bloqueo de Transporte en plantas, ENG 2, SG 5, UY 3, y de Intercambio de gases en animales, ENG 6, SG 5, UY 5); prerrequisito: Membrana celular ← Biomoléculas y Estructuras celulares básicas (confianza alta); T8_27-B2.1 Estructura y funciones de la célula</t>
+          <t>AU 7, CO 4,5, ENG 6, JP 7, SG 5, UY 4 (La célula como unidad de la vida); prerrequisito: Difusión y ósmosis (bloqueo de Transporte en plantas: ENG 2, JP 5, SG 5, UY 3; y de Intercambio de gases en plantas); prerrequisito: Membrana celular ← Biomoléculas y Estructuras celulares básicas (confianza alta); secuencia: Biomoléculas (6.°) ← El carbono y las moléculas orgánicas (11.°), confianza alta; T8_27-B2.1 Estructura y funciones de la célula</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Los países presentan la célula en 4.° o 5.°. La difusión, bloqueo del transporte y del intercambio de gases, llega con lo que necesita: niveles de organización, biomoléculas y partes básicas de la célula, en nivel experimental.</t>
+          <t>La difusión, bloqueo del transporte en plantas, llega a 5.° con lo que necesita: célula, niveles, biomoléculas y estructuras básicas. El tema de biomoléculas incorpora el carbono y corrige una secuencia invertida sin gastar presupuesto.</t>
         </is>
       </c>
     </row>
@@ -592,51 +592,53 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>G06-CIE-U5-5.1</t>
+          <t>G06-CIE-U5-5.2, G08-CIE-U7-7.11</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>6 y 8</t>
+        </is>
       </c>
       <c r="F3" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>7. La célula y la organización de los seres vivos</t>
+          <t>7. La célula y la organización de los seres vivos (5.2, después de biomoléculas) y 8. Funciones vitales de plantas y animales (7.11)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>7.3. Identificación experimental de los grupos de biomoléculas en los alimentos y del carbono como su elemento base.</t>
+          <t>7.4. Experimentación con la acción de las enzimas, proteínas formadas por cadenas de aminoácidos. | 8.5. Experimentación con los procesos químicos y mecánicos que intervienen en la digestión.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Identifica con pruebas sencillas almidón, grasas y proteínas en alimentos y reconoce el carbono como elemento común a todas ellas.</t>
+          <t>Comprueba el efecto de una enzima (la catalasa de la papa) con y sin calor y explica, con un modelo de cuentas, que es una proteína formada por una cadena de aminoácidos. | Comprueba con saliva y almidón (prueba de yodo) la acción de una enzima digestiva y la distingue de la digestión mecánica.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Biomoléculas, El carbono y las moléculas orgánicas</t>
+          <t>Enzimas, Catalizadores, Proteínas: estructura y función, Aminoácidos y estructura de las proteínas, Digestión química y absorción de nutrientes, Sistema digestivo</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: El carbono y las moléculas orgánicas (hoy en 11.°) de Biomoléculas, confianza alta</t>
+          <t>ENG 4, JP 5, SG 4, UY 4 (Digestión química y absorción de nutrientes); bloqueo: Enzimas (6.°) se mueve con la digestión; secuencia: Enzimas ← Proteínas: estructura y función (10.°), confianza alta; Proteínas ← Aminoácidos (confianza alta); prerrequisito: Sistema digestivo (4.°) y Biomoléculas (5.°, acción 1)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Complementa la acción 1: el tema de biomoléculas, ya trasladado a 5.°, incorpora el carbono como base de las moléculas orgánicas y corrige una secuencia invertida de seis grados sin gastar presupuesto.</t>
+          <t>Japón se suma a Inglaterra, Singapur y Uruguay: la digestión química se enseña en 4.° o 5.°. Su bloqueo, las enzimas, sube con ella a 5.°, tras las biomoléculas y presentadas como proteínas.</t>
         </is>
       </c>
     </row>
@@ -685,12 +687,12 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>ENG 2, SG 5, UY 3 (Transporte en plantas: xilema y floema); prerrequisito: Tejidos vegetales ← Diferenciación y especialización celular ← Mitosis y ciclo celular ← ADN y cromosomas (confianza alta, todos en 6.°); prerrequisito: Difusión y ósmosis (5.°, acción 1)</t>
+          <t>ENG 2, JP 5, SG 5, UY 3 (Transporte en plantas: xilema y floema); bloqueo: Tejidos vegetales ← Diferenciación y especialización celular (6.°), confianza alta; prerrequisito: Difusión y ósmosis (5.°, acción 1)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Inglaterra, Singapur y Uruguay lo enseñan entre 2.° y 5.°; El Salvador, en 8.°. Sube a 6.°, no a 5.°, porque los tejidos requieren diferenciación celular y mitosis, que están en 6.°.</t>
+          <t>Cuatro países, tres de alto desempeño, lo enseñan entre 2.° y 5.°; El Salvador, en 8.°. Sube a 6.° y no a 5.° porque los tejidos vegetales requieren la diferenciación celular de 6.°.</t>
         </is>
       </c>
     </row>
@@ -741,12 +743,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Reproducción sexual y asexual (bloqueo de Reproducción sexual de las plantas con flor: ENG 2, UY 3, SG 5, AU 8)</t>
+          <t>prerrequisito: Reproducción sexual y asexual (bloqueo de Reproducción sexual de las plantas con flor: AU 8, ENG 2, JP 4, SG 5, UY 3); ENG 3, SG 5, UY 3 (Reproducción sexual y asexual)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>La propagación asexual introduce el bloqueo de la reproducción de plantas con flor; la germinación cierra el ciclo de la planta. Ambos son prácticas concretas, apropiadas para 5.°, sin prerrequisitos tardíos.</t>
+          <t>La propagación asexual introduce el bloqueo de la reproducción de plantas con flor; la germinación cierra el ciclo de la planta. Son prácticas concretas, apropiadas para 5.°, sin prerrequisitos tardíos.</t>
         </is>
       </c>
     </row>
@@ -795,12 +797,12 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>ENG 2, UY 3, SG 5, AU 8 (Reproducción sexual de las plantas con flor); prerrequisito: Reproducción sexual y asexual (acción 4)</t>
+          <t>AU 8, ENG 2, JP 4, SG 5, UY 3 (Reproducción sexual de las plantas con flor); prerrequisito: Reproducción sexual y asexual (5.°, acción 4)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>El tema mezcla fecundación de plantas con flor (países: 3.° a 5.°) y división celular (requiere mitosis, 6.°). Se separan: solo la fecundación baja a 5.°; la mitosis no se adelanta.</t>
+          <t>El tema mezcla fecundación de plantas con flor (Japón la enseña en 4.°, Inglaterra en 2.°) y división celular (requiere mitosis, 6.°). Solo la fecundación baja a 5.°.</t>
         </is>
       </c>
     </row>
@@ -815,46 +817,46 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U7-7.9, G08-CIE-U7-7.7, G08-CIE-U7-7.8, G08-CIE-U7-7.10</t>
+          <t>G07-CIE-U4-4.1, G07-CIE-U4-4.2, G07-CIE-U4-4.5</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>8. Funciones vitales de plantas y animales</t>
+          <t>9. Interacciones en los ecosistemas</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>8.4. Modelaje de una estructura respiratoria. | 8.5. Demostración práctica del vínculo entre el intercambio de gases y la circulación. | 8.6. Reconocimiento de las estructuras respiratorias y circulatorias del ser humano y de otros vertebrados. | 8.7. Exploración de la estructura y las funciones del sistema digestivo humano.</t>
+          <t>9.1. Identificación de interacciones ecológicas a partir de contextos prácticos. | 9.2. Descripción de interacciones ecológicas observadas en contextos prácticos. | 9.3. Identificación de productores, consumidores y descomponedores en las redes tróficas de un ecosistema local.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Construye un modelo de pulmón (botella y globos) y explica la entrada y salida de aire. | Explica con un esquema cómo la sangre lleva el oxígeno de los pulmones a las células y el dióxido de carbono de vuelta. | Compara con imágenes o modelos pulmones, branquias y corazón en peces, aves y mamíferos. | Ubica en un modelo los órganos del sistema digestivo y describe qué ocurre con el alimento en cada uno.</t>
+          <t>Clasifica ejemplos locales como competencia, depredación, mutualismo, comensalismo o parasitismo. | Describe una interacción observada (en la escuela o en un video) indicando qué gana o pierde cada especie. | Construye una red trófica de un ecosistema local y explica qué pasaría si desapareciera una especie.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Intercambio de gases en animales, Sistema respiratorio, Sistema circulatorio, Sistema digestivo</t>
+          <t>Competencia por recursos, Depredación, Relaciones intraespecíficas, Simbiosis: mutualismo, comensalismo y parasitismo, Productores, consumidores y descomponedores, Redes tróficas</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>ENG 6, SG 5, UY 5 (Intercambio de gases en animales); ENG 4, SG 4, UY 4 (Digestión química y absorción de nutrientes); prerrequisito: Difusión y ósmosis (acción 1)</t>
+          <t>CO 3, ENG 2, JP 5 (Depredación); CO 3, UY 6 (Relaciones intraespecíficas); prerrequisito: Cadena alimentaria (4.°) de Depredación, confianza alta</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Los países de alto desempeño enseñan respiración, circulación y digestión entre 4.° y 6.°; El Salvador, en 8.°. Se adelantan los sistemas; su único bloqueo, la difusión, llega a 5.° en la acción 1.</t>
+          <t>Con Japón, la depredación tiene dos países de alto desempeño (ENG 2, JP 5); El Salvador la enseña en 7.°. 4.1 y 4.2 bajan juntos; 4.5 da las redes tróficas que usa el flujo de energía en 6.°.</t>
         </is>
       </c>
     </row>
@@ -864,51 +866,51 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G07-CIE-U4-4.1, G07-CIE-U4-4.2, G07-CIE-U4-4.5</t>
+          <t>G08-CIE-U6-6.10, G08-CIE-U6-6.12</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>9. Interacciones en los ecosistemas</t>
+          <t>5. Célula. (después de 5.12 y 5.17)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9.1. Identificación de interacciones ecológicas a partir de contextos prácticos. | 9.2. Descripción de interacciones ecológicas observadas en contextos prácticos. | 9.3. Identificación de productores, consumidores y descomponedores en las redes tróficas de un ecosistema local.</t>
+          <t>5.23. Indagación del intercambio de gases en las hojas y su relación con la fotosíntesis y la respiración.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Clasifica ejemplos locales como competencia, depredación, mutualismo, comensalismo o parasitismo. | Describe una interacción observada (en la escuela o en un video) indicando qué gana o pierde cada especie. | Construye una red trófica de un ecosistema local y explica qué pasaría si desapareciera una especie.</t>
+          <t>Explica, con evidencias de un experimento con hojas, qué gases entran y salen de día y de noche y lo relaciona con la fotosíntesis y la respiración.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Competencia por recursos, Depredación, Relaciones intraespecíficas, Simbiosis: mutualismo, comensalismo y parasitismo, Productores, consumidores y descomponedores, Redes tróficas</t>
+          <t>Intercambio de gases en plantas, Fotosíntesis, Partes de la planta y sus funciones</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>CO 3, ENG 6 (Competencia por recursos); CO 3, ENG 2 (Depredación); CO 3, UY 6 (Relaciones intraespecíficas); prerrequisito: Competencia por recursos (bloqueo, se mueve en 4.1)</t>
+          <t>ENG 6, JP 7, SG 5, UY 5 (Intercambio de gases en plantas); bloqueos: Fotosíntesis y Respiración celular (6.°); Difusión y ósmosis (5.°, acción 1)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Colombia e Inglaterra introducen competencia y depredación entre 2.° y 6.°. 4.1 y 4.2 se mueven juntos para que la competencia (bloqueo) llegue con la simbiosis; 4.5 prepara el flujo de energía.</t>
+          <t>6.10 y 6.12 trabajan las funciones de la hoja. Unidas suben a 6.°, el primer grado posible tras fotosíntesis y respiración; la mediana de alto desempeño es 6. Libera un tema para la división 5.</t>
         </is>
       </c>
     </row>
@@ -923,46 +925,46 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>G08-CIE-U6-6.10, G08-CIE-U6-6.12</t>
+          <t>G06-CIE-U5-5.19, G06-CIE-U5-5.20, G06-CIE-U5-5.22</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>5. Célula. (después de 5.12 y 5.17)</t>
+          <t>5. Célula.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>5.23. Indagación del intercambio de gases en las hojas y su relación con la fotosíntesis y la respiración.</t>
+          <t>5.19. Descripción de la estructura y las funciones de la matriz extracelular en los tejidos y de sus alteraciones en lesiones.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Explica, con evidencias de un experimento con hojas, qué gases entran y salen de día y de noche y lo relaciona con la fotosíntesis y la respiración.</t>
+          <t>Describe la composición de la matriz extracelular, explica su función en un tejido observado al microscopio y la relaciona con un caso de lesión.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Intercambio de gases en plantas, Fotosíntesis, Partes de la planta y sus funciones</t>
+          <t>Diferenciación y especialización celular</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>ENG 6, SG 5, UY 5 (Intercambio de gases en plantas); prerrequisito: Fotosíntesis y Respiración celular (6.°); prerrequisito: Difusión y ósmosis (acción 1)</t>
+          <t>fusión: los tres temas trabajan Diferenciación y especialización celular (matriz extracelular)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>6.10 y 6.12 trabajan las funciones de la hoja. Unidas suben a 6.°, el primer grado posible tras fotosíntesis y respiración. Libera el tema que necesita la división de G06-6.8 (acción 5).</t>
+          <t>Descripción, observación y revisión documental de la matriz extracelular son el mismo contenido en tres temas. La fusión libera dos temas: célula animal y vegetal (acción 9) y ciclos del carbono y del oxígeno (acción 11).</t>
         </is>
       </c>
     </row>
@@ -972,51 +974,45 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>G06-CIE-U5-5.19, G06-CIE-U5-5.20</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
       <c r="D10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>6</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
       <c r="F10" s="2" t="n">
         <v>6</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5. Célula.</t>
+          <t>5. Célula. (después de 5.11)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5.19. Descripción de la estructura y las funciones de la matriz extracelular en los tejidos.</t>
+          <t>5.24. Comparación de la célula animal y la célula vegetal mediante observación al microscopio.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Describe la composición de la matriz extracelular y explica su función en un tejido observado al microscopio.</t>
+          <t>Elabora un cuadro comparativo de pared celular, cloroplastos y vacuola a partir de sus propias preparaciones de epidermis de cebolla y mucosa bucal.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Diferenciación y especialización celular</t>
+          <t>Célula animal y célula vegetal</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Diferenciación y especialización celular (matriz extracelular)</t>
+          <t>AU 7, CO 6,5, ENG 6, JP 7, UY 7 (Célula animal y célula vegetal); prerrequisito: Estructuras celulares básicas (5.°, acción 1); secuencia: Organelos de la célula eucariota (6.°) ← Célula animal y célula vegetal (11.°); T8_27-B2.1 Estructura y funciones de la célula</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>Descripción y observación de la matriz extracelular son dos caras del mismo contenido. La fusión libera un tema para pagar la célula animal y vegetal (acción 10).</t>
+          <t>Hoy solo aparece en 11.°. Cinco países la enseñan entre 6.° y 7.° (Japón en 7.°). Va en 6.°, un grado antes que la mediana, porque los organelos de 6.° la necesitan. Se paga con la fusión 8.</t>
         </is>
       </c>
     </row>
@@ -1026,45 +1022,51 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr"/>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>G07-CIE-U2-2.4, G07-CIE-U2-2.5, G07-CIE-U2-2.6</t>
+        </is>
+      </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="F11" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5. Célula.</t>
+          <t>2. Genética y evolución</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>5.24. Comparación de la célula animal y la célula vegetal mediante observación al microscopio.</t>
+          <t>2.4. Simulación y explicación de la replicación del ADN a partir de fenómenos cotidianos.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Elabora un cuadro comparativo de pared celular, cloroplastos y vacuola a partir de sus propias preparaciones de epidermis de cebolla y mucosa bucal.</t>
+          <t>Simula con un modelo la replicación del ADN, la relaciona con el crecimiento o la cicatrización y la explica con un recurso propio (esquema, video o maqueta).</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Célula animal y célula vegetal</t>
+          <t>Estructura del ADN, Replicación del ADN, Mitosis y ciclo celular</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>AU 7, CO 6,5, ENG 6, UY 7 (Célula animal y célula vegetal); prerrequisito: Estructuras celulares básicas (5.°, acción 1); T8_27-B2.1 Estructura y funciones de la célula</t>
+          <t>fusión: los tres temas trabajan Replicación del ADN</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Hoy solo aparece en 11.° (G11-BIO-U3-3.3). Inglaterra lo enseña en 6.° y Australia y Uruguay en 7.°. Va en 6.° después de las partes básicas de la célula. Se paga con la fusión 9.</t>
+          <t>La malla dedica tres temas consecutivos a la replicación del ADN. Unirlos libera dos temas (herencia de rasgos y adaptaciones conductuales en 5.°) y alivia 7.°, el grado más cargado.</t>
         </is>
       </c>
     </row>
@@ -1074,51 +1076,45 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>G07-CIE-U2-2.5, G07-CIE-U2-2.6</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
       <c r="D12" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2. Genética y evolución</t>
+          <t>5. Célula. (después de fotosíntesis, respiración y 5.25; o unidad nueva «Energía y materia en los ecosistemas»)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2.5. Simulación y explicación del proceso de replicación del ADN.</t>
+          <t>5.26. Explicación de los ciclos del carbono y del oxígeno a partir de la fotosíntesis y la respiración.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Simula con un modelo la replicación del ADN y la explica con un recurso propio (esquema, video o maqueta).</t>
+          <t>Representa en un esquema cómo la fotosíntesis, la respiración y la descomposición mueven el carbono y el oxígeno entre los seres vivos, el aire y el suelo de un ecosistema local.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Estructura del ADN, Replicación del ADN</t>
+          <t>Ciclos del carbono y del oxígeno</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Replicación del ADN (2.4 también lo trabaja)</t>
+          <t>AU 8, CO 6,5, ENG 6, JP 5 (Ciclos del carbono y del oxígeno); bloqueos: Fotosíntesis y Respiración celular (6.°); T8_27-B5.3 Ciclos del agua, el oxígeno y el carbono (reforzar: 1 tema, débil)</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>La malla dedica tres temas a la replicación del ADN (2.4, 2.5 y 2.6). Unir simulación y elaboración de recursos libera un tema para la acción 12.</t>
+          <t>Con Japón (5.°) e Inglaterra (6.°), el grado destino es 6.°. Sus dos bloqueos ya están en 6.°, así que deja 7.° y va tras la fotosíntesis. Se paga con la fusión 8.</t>
         </is>
       </c>
     </row>
@@ -1128,45 +1124,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>G07-CIE-U5-5.8</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>7</v>
+      </c>
       <c r="F13" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>4. Ecología (después de trabajar el ciclo del agua)</t>
+          <t>5. Recurso hídrico (después del tema del ciclo del agua)</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>4.13. Explicación del papel de los seres vivos en los ciclos del agua, del oxígeno y del carbono.</t>
+          <t>5.8. Reconocimiento del papel de los seres vivos en el ciclo del agua y de los parámetros biológicos de su calidad.</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Representa en un esquema cómo la fotosíntesis, la respiración, la transpiración y la descomposición mueven agua, oxígeno y carbono en un ecosistema local.</t>
+          <t>Explica con un esquema cómo la transpiración, la respiración y la descomposición participan en el ciclo del agua y usa organismos indicadores para valorar la calidad del agua de un río local.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Papel de los seres vivos en el ciclo del agua, Ciclos del carbono y del oxígeno</t>
+          <t>Papel de los seres vivos en el ciclo del agua, Ecosistemas acuáticos y marinos, Calidad y tratamiento del agua</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>CO 6,5, SG 5 (Papel de los seres vivos en el ciclo del agua); CO 6,5, ENG 6 (Ciclos del carbono y del oxígeno); T8_27-B5.3 Ciclos del agua, el oxígeno y el carbono (reforzar: 1 tema, débil); prerrequisito: Ciclo del agua (7.°); Fotosíntesis y Respiración celular (6.°)</t>
+          <t>CO 6,5, JP 5, SG 5 (Papel de los seres vivos en el ciclo del agua); bloqueo: Ciclo del agua (7.°), confianza alta; T8_27-B5.3 Ciclos del agua, el oxígeno y el carbono (reforzar)</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>B5.3 tiene un solo tema débil. Los ciclos del carbono y del oxígeno podrían ir en 6.°, pero el del agua llega en 7.°; se tratan juntos en 7.°, tras ese tema. Se paga con la fusión 11.</t>
+          <t>Japón y Singapur lo enseñan en 5.°, pero el ciclo del agua llega en 7.°. Se integra, sin gastar presupuesto, en el tema de 7.° que ya trabaja el agua y los seres vivos.</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1197,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5. Célula. (después de fotosíntesis y respiración; o unidad nueva «Energía en los ecosistemas»)</t>
+          <t>5. Célula. (después de fotosíntesis y respiración; o unidad nueva «Energía y materia en los ecosistemas»)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1215,12 +1217,12 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>AU 6, CO 6,5, SG 6, UY 6 (Flujo de energía y pirámides ecológicas); T8_27-B5.2 Flujo de energía en los ecosistemas (reforzar: 1 tema, débil); prerrequisito: Redes tróficas (5.°, acción 7)</t>
+          <t>AU 6, CO 6,5, SG 6, UY 6 (Flujo de energía y pirámides ecológicas; oportunidad +1 con alto desempeño); T8_27-B5.2 Flujo de energía en los ecosistemas (reforzar: 1 tema, débil); prerrequisito: Redes tróficas (5.°, acción 6)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Australia, Singapur y Uruguay enseñan el flujo de energía en 6.°; El Salvador, en 7.° (débil) y 10.°. Sube a 6.° reformulado con pirámides, tras las redes tróficas de 5.° y la fotosíntesis de 6.°.</t>
+          <t>Australia y Singapur enseñan el flujo de energía en 6.°; El Salvador, en 7.° con un solo tema débil. Sube a 6.° con pirámides, tras las redes tróficas de 5.° y la fotosíntesis de 6.°.</t>
         </is>
       </c>
     </row>
@@ -1230,51 +1232,51 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>G06-CIE-U5-5.2</t>
+          <t>G08-CIE-U7-7.13, G08-CIE-U7-7.15</t>
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>5. Célula.</t>
+          <t>7. Anatomía y Fisiología Animal</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>5.2. Experimentación con la actividad de las enzimas como proteínas formadas por cadenas de aminoácidos.</t>
+          <t>7.13. Indagación de los procesos y mecanismos de excreción en los animales.</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Comprueba el efecto de una enzima (por ejemplo, la catalasa de la papa) en distintas condiciones y explica que su función depende de su estructura de proteína.</t>
+          <t>Compara los mecanismos de excreción de distintos grupos de animales y los relaciona con el ambiente en que viven.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>Enzimas, Catalizadores, Proteínas: estructura y función, Aminoácidos y estructura de las proteínas</t>
+          <t>Osmorregulación y equilibrio hídrico, Sistema excretor</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>prerrequisito: Proteínas: estructura y función (hoy en 10.°) de Enzimas (6.°), confianza alta; prerrequisito: Aminoácidos y estructura de las proteínas (hoy en 11.°) de Proteínas, confianza alta</t>
+          <t>fusión: ambos temas trabajan Sistema excretor y Osmorregulación (7.14 también)</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>Las enzimas llegan en 6.° antes que las proteínas (10.°). El tema se reformula para presentarlas como proteínas formadas por aminoácidos, sin gastar presupuesto. Prepara la digestión química (acción 15).</t>
+          <t>La excreción ocupa tres temas (7.13, 7.14 y 7.15). Unir procesos generales y mecanismos libera un tema para la homeostasis (acción 15) y conserva la práctica de función renal.</t>
         </is>
       </c>
     </row>
@@ -1284,51 +1286,45 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>mover</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>G08-CIE-U7-7.11</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>6</v>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>5. Célula. (después de 5.2)</t>
+          <t>7. Anatomía y Fisiología Animal (después de excreción)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5.26. Experimentación con los procesos químicos y mecánicos que intervienen en la digestión.</t>
+          <t>7.16. Explicación de la homeostasis y de la regulación hormonal del medio interno.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Comprueba con un experimento (amilasa de la saliva y almidón) la acción de una enzima digestiva y la distingue de la digestión mecánica.</t>
+          <t>Explica con un ejemplo (glucosa en sangre o temperatura corporal) cómo los sistemas excretor y endocrino mantienen el equilibrio interno, e identifica las glándulas que intervienen.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Digestión química y absorción de nutrientes, Enzimas, Sistema digestivo</t>
+          <t>Homeostasis, Sistema endocrino y hormonas</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>ENG 4, SG 4, UY 4 (Digestión química y absorción de nutrientes); prerrequisito: Enzimas (6.°, acción 14); prerrequisito: Sistema digestivo (5.°, acción 6)</t>
+          <t>CO 8, UY 8 (Homeostasis); AU 8, CO 8, UY 8 (Sistema endocrino y hormonas); bloqueo: Homeostasis (10.°) del sistema endocrino; se introduce primero en el mismo tema; secuencia: Osmorregulación (8.°) ← Homeostasis (10.°)</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>Inglaterra, Singapur y Uruguay la enseñan en 4.°; El Salvador, en 8.°. Su bloqueo, las enzimas, ahora está en 6.° (G06-5.2), así que sube a 6.° justo después de ese tema.</t>
+          <t>Australia, Colombia y Uruguay enseñan hormonas en 8.°; El Salvador, en 10.°. Un tema introductorio tras la excreción resuelve el bloqueo de homeostasis. Japón no cambia esta evidencia. Se paga con la fusión 14.</t>
         </is>
       </c>
     </row>
@@ -1338,51 +1334,45 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>G08-CIE-U7-7.13, G08-CIE-U7-7.15</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr"/>
       <c r="D17" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>8</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>7. Anatomía y Fisiología Animal</t>
+          <t>6. Ciencias de la Tierra. (se inserta antes del actual 6.5, que pasa a 6.6)</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>7.13. Indagación de los procesos y mecanismos de excreción en los animales.</t>
+          <t>6.5. Explicación de los fósiles y de la comparación de estructuras como evidencias de los cambios de los seres vivos.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Compara los mecanismos de excreción de distintos grupos de animales y los relaciona con el ambiente en que viven.</t>
+          <t>Compara fósiles de El Salvador o de la región con organismos actuales y explica, con un ejemplo de estructuras parecidas entre vertebrados, qué muestran sobre su parentesco y sus cambios.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>Osmorregulación y equilibrio hídrico, Sistema excretor</t>
+          <t>Evidencias de la evolución, Fósiles y registro fósil</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan Sistema excretor y Osmorregulación (7.14 también)</t>
+          <t>AU 9, CO 2, ENG 4, JP 8 (Evidencias de la evolución); CO 2, ENG 2, JP 5, UY 6 (Fósiles y registro fósil); secuencia: Filogenia y parentesco evolutivo (7.°) ← Evidencias de la evolución (10.°), confianza alta; prerrequisito: Fósiles y registro fósil (5.°) y Grupos de vertebrados (2.°)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>La excreción ocupa tres temas (7.13, 7.14 y 7.15). Unir procesos generales y mecanismos libera un tema para la homeostasis (acción 17).</t>
+          <t>Los fósiles ya están en 5.°, pero las evidencias de la evolución llegan en 10.°, después de la filogenia de 7.°. El tema se centra ahora en las evidencias y corrige esa secuencia. Se paga con la fusión 17.</t>
         </is>
       </c>
     </row>
@@ -1392,45 +1382,51 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr"/>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>G07-CIE-U2-2.2, G07-CIE-U2-2.3</t>
+        </is>
+      </c>
       <c r="D18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="2" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="F18" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7. Anatomía y Fisiología Animal (después de excreción)</t>
+          <t>2. Genética y evolución</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7.16. Explicación de la homeostasis y de la regulación hormonal del medio interno.</t>
+          <t>2.2. Experimentación con técnicas de extracción y tinción de ácidos nucleicos y explicación de su funcionamiento.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Explica con un ejemplo (glucosa en sangre o temperatura corporal) cómo los sistemas excretor y endocrino mantienen el equilibrio interno, e identifica las glándulas que intervienen.</t>
+          <t>Extrae ADN de un vegetal con materiales caseros y explica qué hace cada paso del procedimiento.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Homeostasis, Sistema endocrino y hormonas</t>
+          <t>ADN y cromosomas, Membrana celular</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>CO 8, UY 8 (Homeostasis); AU 8, CO 8, UY 8 (Sistema endocrino y hormonas); prerrequisito: Homeostasis (bloqueo del sistema endocrino, se introduce primero en el mismo tema)</t>
+          <t>fusión: ambos temas trabajan ADN y cromosomas (extracción y tinción de ácidos nucleicos)</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>Australia, Colombia y Uruguay enseñan hormonas en 8.°; El Salvador, en 10.°. Un tema introductorio en 8.°, tras la excreción, resuelve el bloqueo de homeostasis. Se paga con la fusión 16.</t>
+          <t>La práctica de extracción y su explicación son el mismo contenido en dos temas consecutivos. Unirlos libera un tema para las evidencias de la evolución en 5.° (acción 16).</t>
         </is>
       </c>
     </row>
@@ -1453,32 +1449,32 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>6. Ciencias de la Tierra. (se inserta antes del actual 6.5, que pasa a 6.6)</t>
+          <t>8. Funciones vitales de plantas y animales (después de 8.3)</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>6.5. Explicación de la formación de los fósiles y del registro fósil como evidencia de los cambios de los seres vivos.</t>
+          <t>8.4. Descripción de la herencia de rasgos de progenitores a descendientes en plantas y animales.</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Modela la formación de un fósil y explica, con ejemplos de fósiles de El Salvador o de la región, qué muestran sobre los seres vivos del pasado y sus cambios.</t>
+          <t>Compara rasgos de crías y progenitores (fotos de familias de animales, plantas de semillas de un mismo fruto) y distingue los rasgos heredados de los adquiridos.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>Fósiles y registro fósil, Evidencias de la evolución</t>
+          <t>Herencia de rasgos</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>CO 2, ENG 4 (Fósiles y registro fósil); AU 9, CO 2, ENG 4 (Evidencias de la evolución); prerrequisito: Fósiles y registro fósil (hoy en 10.°) de Historia de la vida en la Tierra (5.°, G05-6.5), confianza alta; prerrequisito: Evidencias de la evolución de Filogenia (7.°), confianza alta</t>
+          <t>CO 2, ENG 4, JP 8, SG 5 (Herencia de rasgos); prerrequisito: Ciclo de vida de los animales (3.°); secuencia: ADN y cromosomas (6.°) ← Herencia de rasgos (10.°), confianza media</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>El tema de fósiles de 5.° pasó a Ciencias de la Tierra, y Biología quedó sin fósiles antes de 10.°. Inglaterra los enseña en 4.°. Corrige dos secuencias: historia de la vida y filogenia. Se paga con la fusión 19.</t>
+          <t>Inglaterra y Singapur, de alto desempeño, enseñan la herencia de rasgos en 4.° y 5.°; El Salvador, en 10.°. Llega a 5.°, tras la reproducción, y prepara el ADN de 6.°. Se paga con la fusión 10.</t>
         </is>
       </c>
     </row>
@@ -1488,105 +1484,45 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>G07-CIE-U2-2.2, G07-CIE-U2-2.3</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
       <c r="D20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>7</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2. Genética y evolución</t>
+          <t>9. Interacciones en los ecosistemas (después de 9.3)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2.2. Experimentación con técnicas de extracción y tinción de ácidos nucleicos y explicación de su funcionamiento.</t>
+          <t>9.4. Identificación de adaptaciones conductuales de los animales a su ambiente.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Extrae ADN de un vegetal con materiales caseros y explica qué hace cada paso del procedimiento.</t>
+          <t>Explica con ejemplos locales o de la región (migración de aves, hibernación, vida en grupo, actividad nocturna) cómo una conducta ayuda a un animal a sobrevivir en su ambiente.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>ADN y cromosomas, Membrana celular</t>
+          <t>Adaptaciones conductuales</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>fusión: ambos temas trabajan ADN y cromosomas (extracción y tinción de ácidos nucleicos)</t>
+          <t>AU 4, CO 2, JP 3, SG 6 (Adaptaciones conductuales); prerrequisito: Hábitat y ecosistemas comunes (2.°)</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>La práctica de extracción y su explicación son el mismo contenido en dos temas consecutivos. Unirlos libera un tema para los fósiles de 5.° (acción 18) y alivia 7.°, el grado más cargado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>G07-CIE-U2-2.8</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>2. Genética y evolución</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>2.8. Visualización de polimorfismos y de la variación genética en la descendencia a partir de casos.</t>
-        </is>
-      </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>Explica con casos (familias, cruces o semillas) por qué los descendientes de los mismos progenitores son distintos entre sí.</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Genes y alelos, Variación genética en la descendencia</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>prerrequisito: Variación genética en la descendencia (hoy en 11.°) de Selección natural (7.°), confianza alta; CO 8,5, ENG 4 (Variación genética en la descendencia)</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>La selección natural (2.15) necesita la variación en la descendencia, que el grafo ubica en 11.°. Se hace explícita en 2.8, que ya está en 7.° antes de 2.15, sin gastar presupuesto.</t>
+          <t>Con Japón (3.°), tres países de alto desempeño la enseñan entre 3.° y 6.°; El Salvador, en 11.°. Es el mayor atraso del archivo de candidatos. Se paga con la fusión 10.</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1611,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1698,7 +1634,7 @@
         <v>44</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>
@@ -1721,7 +1657,7 @@
         <v>27</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4">
         <f>C5-B5</f>

--- a/asignaturas/biologia/propuesta/Propuesta_Biologia_G05-G08.xlsx
+++ b/asignaturas/biologia/propuesta/Propuesta_Biologia_G05-G08.xlsx
@@ -628,17 +628,17 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Enzimas, Catalizadores, Proteínas: estructura y función, Aminoácidos y estructura de las proteínas, Digestión química y absorción de nutrientes, Sistema digestivo</t>
+          <t>Enzimas, Proteínas: estructura y función, Aminoácidos y estructura de las proteínas, Digestión química y absorción de nutrientes, Sistema digestivo</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>ENG 4, JP 5, SG 4, UY 4 (Digestión química y absorción de nutrientes); bloqueo: Enzimas (6.°) se mueve con la digestión; secuencia: Enzimas ← Proteínas: estructura y función (10.°), confianza alta; Proteínas ← Aminoácidos (confianza alta); prerrequisito: Sistema digestivo (4.°) y Biomoléculas (5.°, acción 1)</t>
+          <t>ENG 4, JP 5, SG 4, UY 4 (Digestión química y absorción de nutrientes); bloqueo: Enzimas (6.°) se mueve con la digestión; secuencia: Enzimas ← Proteínas: estructura y función (10.°), confianza alta; Proteínas ← Aminoácidos (confianza alta); prerrequisito: Sistema digestivo (4.°) y Biomoléculas (5.°, acción 1); temas_del_ciclo: G06-5.2 etiquetado con Catalizadores (Química, 6.°) antes de su prerrequisito Energía de activación y perfil energético (10.°); el tema muestra la acción de una enzima, no la catálisis a nivel químico</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Japón se suma a Inglaterra, Singapur y Uruguay: la digestión química se enseña en 4.° o 5.°. Su bloqueo, las enzimas, sube con ella a 5.°, tras las biomoléculas y presentadas como proteínas.</t>
+          <t>Japón se suma a Inglaterra, Singapur y Uruguay: la digestión química se enseña en 4.° o 5.°. Su bloqueo, las enzimas, sube con ella a 5.°, tras las biomoléculas y presentadas como proteínas. Se retira la etiqueta de catalizadores: el tema comprueba que la enzima acelera un proceso, sin energía de activación, que es lo que define el concepto químico.</t>
         </is>
       </c>
     </row>
